--- a/output/pdf_financials_xlsx/SOMA.xlsx
+++ b/output/pdf_financials_xlsx/SOMA.xlsx
@@ -1210,16 +1210,16 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.353595</v>
+        <v>-0.353595</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>1.464523</v>
+        <v>-1.464523</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>3.390641</v>
+        <v>-3.390641</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.383976</v>
+        <v>-0.383976</v>
       </c>
       <c r="G16" s="3" t="n">
         <v>-0.942372</v>
@@ -1482,16 +1482,16 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.353595</v>
+        <v>-0.353595</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1.464523</v>
+        <v>-1.464523</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>3.390641</v>
+        <v>-3.390641</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>0.383976</v>
+        <v>-0.383976</v>
       </c>
       <c r="G20" s="3" t="n">
         <v>-0.942372</v>
@@ -1644,16 +1644,16 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>0.353595</v>
+        <v>-0.353595</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>1.464523</v>
+        <v>-1.464523</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>3.390641</v>
+        <v>-3.390641</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>0.383976</v>
+        <v>-0.383976</v>
       </c>
       <c r="G23" s="3" t="n">
         <v>-0.942372</v>
@@ -1826,16 +1826,16 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>-0.199771</v>
+        <v>0.199771</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>-14.64523</v>
+        <v>14.64523</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>-5.651068</v>
+        <v>5.651068</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>-6.3996</v>
+        <v>6.3996</v>
       </c>
       <c r="G26" s="3" t="n">
         <v>31.4124</v>
@@ -1884,16 +1884,16 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0.353595</v>
+        <v>-0.353595</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>1.464523</v>
+        <v>-1.464523</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>3.390641</v>
+        <v>-3.390641</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>0.383976</v>
+        <v>-0.383976</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>-0.942372</v>
@@ -1992,16 +1992,16 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.353595</v>
+        <v>-0.353595</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>1.464523</v>
+        <v>-1.464523</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>3.390641</v>
+        <v>-3.390641</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.383976</v>
+        <v>-0.383976</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>-0.942372</v>
@@ -2118,16 +2118,16 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G31" s="3" t="n">
         <v>-0</v>
@@ -6015,10 +6015,10 @@
         <v>-0.469487</v>
       </c>
       <c r="J103" s="3" t="n">
-        <v>0</v>
+        <v>-0.145907</v>
       </c>
       <c r="K103" s="3" t="n">
-        <v>0</v>
+        <v>0.1376</v>
       </c>
       <c r="L103" s="3" t="n">
         <v>0</v>
@@ -8370,7 +8370,11 @@
           <t>Prepaids and deposits 8</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>-</t>
@@ -16018,7 +16022,11 @@
           <t>Prepaids and deposits 11</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr"/>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E93" t="inlineStr">
         <is>
           <t>-</t>
@@ -18028,7 +18036,11 @@
           <t>Prepaids and deposits 10</t>
         </is>
       </c>
-      <c r="D115" t="inlineStr"/>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E115" t="inlineStr">
         <is>
           <t>-</t>
@@ -26952,7 +26964,11 @@
           <t>Prepaid and deposits 5</t>
         </is>
       </c>
-      <c r="D213" t="inlineStr"/>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E213" t="inlineStr">
         <is>
           <t>-</t>
@@ -41062,7 +41078,11 @@
           <t>Prepaids and deposits</t>
         </is>
       </c>
-      <c r="D369" t="inlineStr"/>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E369" t="inlineStr">
         <is>
           <t>-</t>
@@ -64636,16 +64656,16 @@
         </is>
       </c>
       <c r="G631" s="5" t="n">
-        <v>1.464523</v>
+        <v>-1.464523</v>
       </c>
       <c r="H631" s="5" t="n">
-        <v>3.390641</v>
+        <v>-3.390641</v>
       </c>
       <c r="I631" s="5" t="n">
-        <v>0.383976</v>
+        <v>-0.383976</v>
       </c>
       <c r="J631" s="5" t="n">
-        <v>0.893972</v>
+        <v>-0.893972</v>
       </c>
       <c r="K631" t="inlineStr">
         <is>
@@ -64824,10 +64844,10 @@
         </is>
       </c>
       <c r="I633" s="5" t="n">
-        <v>0.307998</v>
+        <v>-0.307998</v>
       </c>
       <c r="J633" s="5" t="n">
-        <v>0.942372</v>
+        <v>-0.942372</v>
       </c>
       <c r="K633" t="inlineStr">
         <is>
@@ -65726,13 +65746,13 @@
         </is>
       </c>
       <c r="G643" s="5" t="n">
-        <v>1.44862</v>
+        <v>-1.44862</v>
       </c>
       <c r="H643" s="5" t="n">
-        <v>3.457932</v>
+        <v>-3.457932</v>
       </c>
       <c r="I643" s="5" t="n">
-        <v>0.307998</v>
+        <v>-0.307998</v>
       </c>
       <c r="J643" t="inlineStr">
         <is>
@@ -66914,10 +66934,10 @@
         </is>
       </c>
       <c r="F656" s="5" t="n">
-        <v>0.353595</v>
+        <v>-0.353595</v>
       </c>
       <c r="G656" s="5" t="n">
-        <v>1.464523</v>
+        <v>-1.464523</v>
       </c>
       <c r="H656" t="inlineStr">
         <is>
@@ -67098,10 +67118,10 @@
         </is>
       </c>
       <c r="F658" s="5" t="n">
-        <v>0.353595</v>
+        <v>-0.353595</v>
       </c>
       <c r="G658" s="5" t="n">
-        <v>1.44862</v>
+        <v>-1.44862</v>
       </c>
       <c r="H658" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/SOMA.xlsx
+++ b/output/pdf_financials_xlsx/SOMA.xlsx
@@ -2254,31 +2254,31 @@
         <v>0</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.011898</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.004652</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.083153</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.022882</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.955107</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.104233</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.389446</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.045149</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>2.418987</v>
       </c>
       <c r="M34" s="3" t="n">
         <v>0.529667</v>
@@ -2290,7 +2290,7 @@
         <v>7.840109</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>6.301514</v>
       </c>
     </row>
     <row r="35">
@@ -2362,31 +2362,31 @@
         <v>0</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.011898</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.004652</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.083153</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.022882</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.955107</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.104233</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>3.383216</v>
+        <v>3.772662</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.045149</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>2.418987</v>
       </c>
       <c r="M36" s="3" t="n">
         <v>0.529667</v>
@@ -2398,7 +2398,7 @@
         <v>7.840109</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>1.668732</v>
+        <v>7.970246</v>
       </c>
     </row>
     <row r="37">
@@ -3010,31 +3010,31 @@
         <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.09837</v>
+        <v>0.08647199999999999</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.004652</v>
+        <v>0</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.083153</v>
+        <v>0</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.036132</v>
+        <v>0.01325</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>1.373985</v>
+        <v>0.418878</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.769277</v>
+        <v>0.665044</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>1.228114</v>
+        <v>0.838668</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>28.190037</v>
+        <v>28.144888</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>5.503897</v>
+        <v>3.08491</v>
       </c>
       <c r="M48" s="3" t="n">
         <v>0.713248</v>
@@ -3046,7 +3046,7 @@
         <v>1.496833</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>12.570388</v>
+        <v>6.268874</v>
       </c>
     </row>
     <row r="49">
@@ -7158,16 +7158,16 @@
         <v>0</v>
       </c>
       <c r="M124" s="3" t="n">
-        <v>0</v>
+        <v>-0.169169</v>
       </c>
       <c r="N124" s="3" t="n">
-        <v>0</v>
+        <v>-0.361692</v>
       </c>
       <c r="O124" s="3" t="n">
-        <v>0</v>
+        <v>-0.38581</v>
       </c>
       <c r="P124" s="3" t="n">
-        <v>0</v>
+        <v>-0.669431</v>
       </c>
     </row>
     <row r="125">
@@ -7212,16 +7212,16 @@
         <v>0</v>
       </c>
       <c r="M125" s="3" t="n">
-        <v>0</v>
+        <v>-0.169169</v>
       </c>
       <c r="N125" s="3" t="n">
-        <v>0</v>
+        <v>-0.361692</v>
       </c>
       <c r="O125" s="3" t="n">
-        <v>0</v>
+        <v>-0.38581</v>
       </c>
       <c r="P125" s="3" t="n">
-        <v>0</v>
+        <v>-0.669431</v>
       </c>
     </row>
     <row r="126">
@@ -7935,7 +7935,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -31969,7 +31969,11 @@
           <t>Lease payments 14</t>
         </is>
       </c>
-      <c r="D268" t="inlineStr"/>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E268" t="inlineStr">
         <is>
           <t>-</t>
@@ -34159,7 +34163,11 @@
           <t>Lease payments 13</t>
         </is>
       </c>
-      <c r="D292" t="inlineStr"/>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E292" t="inlineStr">
         <is>
           <t>-</t>
@@ -37116,7 +37124,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D325" t="inlineStr"/>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E325" t="inlineStr">
         <is>
           <t>-</t>
@@ -58142,7 +58154,7 @@
       </c>
       <c r="D559" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E559" t="inlineStr">
@@ -63265,7 +63277,7 @@
       </c>
       <c r="D616" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E616" t="inlineStr">
@@ -64460,7 +64472,7 @@
       </c>
       <c r="D629" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E629" t="inlineStr">
@@ -66373,7 +66385,7 @@
       </c>
       <c r="D650" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E650" t="inlineStr">

--- a/output/pdf_financials_xlsx/SOMA.xlsx
+++ b/output/pdf_financials_xlsx/SOMA.xlsx
@@ -1228,13 +1228,13 @@
         <v>-2.208699</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>-10.388618</v>
+        <v>-10.140658</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>-10.692817</v>
+        <v>-9.673572</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>-38.407849</v>
+        <v>-34.617839</v>
       </c>
       <c r="L16" s="3" t="n">
         <v>4.333576</v>
@@ -1282,13 +1282,13 @@
         <v>0.003766</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.24796</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>-0</v>
+        <v>-1.019245</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>-0</v>
+        <v>-3.79001</v>
       </c>
       <c r="L17" s="3" t="n">
         <v>2.207568</v>
@@ -1902,13 +1902,13 @@
         <v>-2.208699</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-10.388618</v>
+        <v>-10.140658</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-10.692817</v>
+        <v>-9.673572</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-38.407849</v>
+        <v>-34.617839</v>
       </c>
       <c r="L27" s="3" t="n">
         <v>4.333576</v>
@@ -2010,13 +2010,13 @@
         <v>-2.201949</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-10.333912</v>
+        <v>-10.085952</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-10.661018</v>
+        <v>-9.641773000000001</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-38.385467</v>
+        <v>-34.595457</v>
       </c>
       <c r="L29" s="3" t="n">
         <v>5.501089</v>
@@ -2136,13 +2136,13 @@
         <v>-0.1705076155691654</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>-0</v>
+        <v>-2.445206218373601</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>-0</v>
+        <v>-10.53638717942038</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>-0</v>
+        <v>-10.9481415058866</v>
       </c>
       <c r="L31" s="3" t="n">
         <v>50.94102422572028</v>
@@ -3927,22 +3927,22 @@
         <v>0</v>
       </c>
       <c r="K64" s="3" t="n">
-        <v>0</v>
+        <v>2.046901</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>0</v>
+        <v>2.756142</v>
       </c>
       <c r="M64" s="3" t="n">
-        <v>0</v>
+        <v>6.992314</v>
       </c>
       <c r="N64" s="3" t="n">
-        <v>0</v>
+        <v>7.358866</v>
       </c>
       <c r="O64" s="3" t="n">
-        <v>0</v>
+        <v>7.133008</v>
       </c>
       <c r="P64" s="3" t="n">
-        <v>0</v>
+        <v>13.175722</v>
       </c>
     </row>
     <row r="65">
@@ -4146,19 +4146,19 @@
         <v>2.894005</v>
       </c>
       <c r="L68" s="3" t="n">
-        <v>8.725422999999999</v>
+        <v>11.481565</v>
       </c>
       <c r="M68" s="3" t="n">
-        <v>10.517315</v>
+        <v>17.509629</v>
       </c>
       <c r="N68" s="3" t="n">
-        <v>16.156963</v>
+        <v>23.515829</v>
       </c>
       <c r="O68" s="3" t="n">
-        <v>11.609424</v>
+        <v>18.742432</v>
       </c>
       <c r="P68" s="3" t="n">
-        <v>19.50505</v>
+        <v>32.680772</v>
       </c>
     </row>
     <row r="69">
@@ -4524,19 +4524,19 @@
         <v>33.853999</v>
       </c>
       <c r="L75" s="3" t="n">
-        <v>0.229521</v>
+        <v>0</v>
       </c>
       <c r="M75" s="3" t="n">
-        <v>0.659215</v>
+        <v>0</v>
       </c>
       <c r="N75" s="3" t="n">
-        <v>5.062255</v>
+        <v>0</v>
       </c>
       <c r="O75" s="3" t="n">
-        <v>5.48581</v>
+        <v>0</v>
       </c>
       <c r="P75" s="3" t="n">
-        <v>3.971519</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -4691,16 +4691,16 @@
         <v>0</v>
       </c>
       <c r="M78" s="3" t="n">
-        <v>0</v>
+        <v>0.274908</v>
       </c>
       <c r="N78" s="3" t="n">
-        <v>0</v>
+        <v>0.347636</v>
       </c>
       <c r="O78" s="3" t="n">
-        <v>0</v>
+        <v>0.899969</v>
       </c>
       <c r="P78" s="3" t="n">
-        <v>0</v>
+        <v>0.751104</v>
       </c>
     </row>
     <row r="79">
@@ -4745,16 +4745,16 @@
         <v>0</v>
       </c>
       <c r="M79" s="3" t="n">
-        <v>0</v>
+        <v>0.274908</v>
       </c>
       <c r="N79" s="3" t="n">
-        <v>0</v>
+        <v>0.347636</v>
       </c>
       <c r="O79" s="3" t="n">
-        <v>0</v>
+        <v>0.899969</v>
       </c>
       <c r="P79" s="3" t="n">
-        <v>0</v>
+        <v>0.751104</v>
       </c>
     </row>
     <row r="80">
@@ -4812,25 +4812,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M80" s="3" t="n">
+        <v>0.09940406304543635</v>
+      </c>
+      <c r="N80" s="3" t="n">
+        <v>0.02456164893620779</v>
+      </c>
+      <c r="O80" s="3" t="n">
+        <v>0.05638214982393441</v>
+      </c>
+      <c r="P80" s="3" t="n">
+        <v>0.01689654863680829</v>
       </c>
     </row>
     <row r="81">
@@ -5091,16 +5083,16 @@
         <v>20.810951</v>
       </c>
       <c r="M85" s="3" t="n">
-        <v>36.033477</v>
+        <v>35.758569</v>
       </c>
       <c r="N85" s="3" t="n">
-        <v>37.598284</v>
+        <v>37.250648</v>
       </c>
       <c r="O85" s="3" t="n">
-        <v>43.381701</v>
+        <v>42.481732</v>
       </c>
       <c r="P85" s="3" t="n">
-        <v>35.4987</v>
+        <v>34.747596</v>
       </c>
     </row>
     <row r="86">
@@ -5889,13 +5881,13 @@
         <v>0</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>0</v>
+        <v>-0.014866</v>
       </c>
       <c r="E101" s="3" t="n">
-        <v>0</v>
+        <v>-0.006435</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>0</v>
+        <v>0.038212</v>
       </c>
       <c r="G101" s="3" t="n">
         <v>0.010641</v>
@@ -6441,16 +6433,16 @@
         <v>0</v>
       </c>
       <c r="H111" s="3" t="n">
-        <v>0</v>
+        <v>-0.224083</v>
       </c>
       <c r="I111" s="3" t="n">
-        <v>0</v>
+        <v>-0.665623</v>
       </c>
       <c r="J111" s="3" t="n">
-        <v>0</v>
+        <v>-0.832748</v>
       </c>
       <c r="K111" s="3" t="n">
-        <v>0</v>
+        <v>-1.023063</v>
       </c>
       <c r="L111" s="3" t="n">
         <v>0</v>
@@ -7717,16 +7709,16 @@
         <v>0</v>
       </c>
       <c r="H134" s="3" t="n">
-        <v>0</v>
+        <v>-0.224083</v>
       </c>
       <c r="I134" s="3" t="n">
-        <v>0</v>
+        <v>-0.665623</v>
       </c>
       <c r="J134" s="3" t="n">
-        <v>0</v>
+        <v>-0.832748</v>
       </c>
       <c r="K134" s="3" t="n">
-        <v>0</v>
+        <v>-1.023063</v>
       </c>
       <c r="L134" s="3" t="n">
         <v>0</v>
@@ -7773,16 +7765,16 @@
         <v>-0.319227</v>
       </c>
       <c r="H135" s="3" t="n">
-        <v>-2.326754</v>
+        <v>-2.550837</v>
       </c>
       <c r="I135" s="3" t="n">
-        <v>-6.398944</v>
+        <v>-7.064567</v>
       </c>
       <c r="J135" s="3" t="n">
-        <v>-10.774949</v>
+        <v>-11.607697</v>
       </c>
       <c r="K135" s="3" t="n">
-        <v>-42.197859</v>
+        <v>-43.220922</v>
       </c>
       <c r="L135" s="3" t="n">
         <v>6.541144</v>
@@ -9675,7 +9667,11 @@
           <t>Lease obligations 14</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LongTermCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
           <t>-</t>
@@ -11815,7 +11811,11 @@
           <t>Lease obligations 13</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LongTermCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E46" t="inlineStr">
         <is>
           <t>-</t>
@@ -30149,7 +30149,11 @@
           <t>Deferred income tax expense (recovery) 26</t>
         </is>
       </c>
-      <c r="D248" t="inlineStr"/>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E248" t="inlineStr">
         <is>
           <t>-</t>
@@ -31601,7 +31605,11 @@
           <t>Proceeds from private placement 22</t>
         </is>
       </c>
-      <c r="D264" t="inlineStr"/>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E264" t="inlineStr">
         <is>
           <t>-</t>
@@ -33350,7 +33358,11 @@
           <t>Deferred income tax recovery 24</t>
         </is>
       </c>
-      <c r="D283" t="inlineStr"/>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E283" t="inlineStr">
         <is>
           <t>-</t>
@@ -35605,7 +35617,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D308" t="inlineStr"/>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E308" t="inlineStr">
         <is>
           <t>-</t>
@@ -41687,7 +41703,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D376" t="inlineStr"/>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E376" t="inlineStr">
         <is>
           <t>-</t>
@@ -47253,7 +47273,11 @@
           <t>GST Receivable</t>
         </is>
       </c>
-      <c r="D438" t="inlineStr"/>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E438" t="inlineStr">
         <is>
           <t>-</t>
@@ -48610,7 +48634,11 @@
           <t>Shares issued for cash</t>
         </is>
       </c>
-      <c r="D453" t="inlineStr"/>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E453" t="inlineStr">
         <is>
           <t>-</t>
@@ -49807,7 +49835,11 @@
           <t>HST receivable</t>
         </is>
       </c>
-      <c r="D466" t="inlineStr"/>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E466" t="inlineStr">
         <is>
           <t>-</t>
@@ -55013,7 +55045,11 @@
           <t>Earnings from mine operations</t>
         </is>
       </c>
-      <c r="D524" t="inlineStr"/>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
       <c r="E524" t="inlineStr">
         <is>
           <t>-</t>
@@ -55925,7 +55961,11 @@
           <t>Deferred income tax recovery 26</t>
         </is>
       </c>
-      <c r="D534" t="inlineStr"/>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E534" t="inlineStr">
         <is>
           <t>-</t>
@@ -58876,7 +58916,11 @@
           <t>Deferred income tax recovery 19</t>
         </is>
       </c>
-      <c r="D567" t="inlineStr"/>
+      <c r="D567" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E567" t="inlineStr">
         <is>
           <t>-</t>
@@ -62274,7 +62318,11 @@
           <t>Deferred income tax recovery (expense) 19</t>
         </is>
       </c>
-      <c r="D605" t="inlineStr"/>
+      <c r="D605" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E605" t="inlineStr">
         <is>
           <t>-</t>
